--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119918205</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119918205</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103021</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119918205</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126267898</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ängen, Västra Skedvi sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536931</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6606742</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Skedvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>11 blommande på ca 20 m2</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Zetterberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Zetterberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126267898</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126267898</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56823-2022 artfynd.xlsx
+++ b/artfynd/A 56823-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126267898</v>
       </c>
       <c r="B3" t="n">
-        <v>98389</v>
+        <v>98398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
